--- a/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
+++ b/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
@@ -553,6 +553,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -725,6 +726,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="5" t="inlineStr">
@@ -844,6 +846,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="5" t="inlineStr">
@@ -980,6 +983,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="5" t="inlineStr">
@@ -1095,6 +1099,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
         <is>
@@ -1128,6 +1133,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="16" t="inlineStr">
         <is>
@@ -1173,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1196,6 +1202,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -1293,6 +1300,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
@@ -1372,6 +1380,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
@@ -1412,7 +1421,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Saving over the 36-month agreement</t>
+          <t>Saving on the monthly bill over 36 months</t>
         </is>
       </c>
       <c r="C20" s="23">
@@ -1420,6 +1429,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -1437,6 +1447,79 @@
         <is>
           <t>Payable once the link is installed</t>
         </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>The 36-month agreement, with the build included</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Saving on the monthly bill over 36 months</t>
+        </is>
+      </c>
+      <c r="C25" s="15">
+        <f>C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Less: network build, paid up front (incl. VAT)</t>
+        </is>
+      </c>
+      <c r="C26" s="15">
+        <f>-'Detailed Cost Schedule'!E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Less: Vodacom once-off connection fee (incl. VAT)</t>
+        </is>
+      </c>
+      <c r="C27" s="15">
+        <f>-C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Net position at the end of the 36 months — build fully paid, network owned</t>
+        </is>
+      </c>
+      <c r="C28" s="21">
+        <f>SUM(C25:C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Build and connection fee recovered from the saving after (months)</t>
+        </is>
+      </c>
+      <c r="C29" s="24">
+        <f>-(C26+C27)/C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Every year after that, at today's prices</t>
+        </is>
+      </c>
+      <c r="C30" s="15">
+        <f>C17*12</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
+++ b/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
@@ -127,13 +127,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,15 +149,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -549,11 +545,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CTTX Services (Pty) Ltd · Prepared for Barefoot Addo Elephant Lodge (Pty) Ltd · 29 September 2026 · All prices in ZAR, excluding VAT unless stated · Valid 30 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>CTTX Services (Pty) Ltd · Prepared for Barefoot Addo Elephant Lodge (Pty) Ltd · 29 September 2026 · ZAR, excluding VAT unless stated · Valid 30 days</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -590,7 +585,7 @@
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>A. Backbone — mast, base station and power</t>
+          <t>Backbone — mast, base station and power</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -611,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>25943.84</v>
+        <v>25031.83</v>
       </c>
       <c r="E6" s="9">
         <f>C6*D6</f>
@@ -636,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9988.379999999999</v>
+        <v>9637.26</v>
       </c>
       <c r="E7" s="9">
         <f>C7*D7</f>
@@ -644,7 +639,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Two sectors covering the whole property</t>
+          <t>Two sectors cover the whole property</t>
         </is>
       </c>
     </row>
@@ -661,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>3784.26</v>
+        <v>3651.23</v>
       </c>
       <c r="E8" s="9">
         <f>C8*D8</f>
@@ -682,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>9434.129999999999</v>
+        <v>9102.49</v>
       </c>
       <c r="E9" s="9">
         <f>C9*D9</f>
@@ -703,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>30602.91</v>
+        <v>29527.12</v>
       </c>
       <c r="E10" s="9">
         <f>C10*D10</f>
@@ -718,7 +713,7 @@
     <row r="11">
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Subtotal — A. Backbone — mast, base station and power</t>
+          <t>Subtotal — Backbone — mast, base station and power</t>
         </is>
       </c>
       <c r="E11" s="12">
@@ -726,12 +721,11 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>B. Distribution — wireless links to buildings</t>
+          <t>Distribution — wireless links to buildings</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -745,14 +739,14 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cambium ePMP Force 4525L subscriber radio, 25 dBi — main lodge, villas, spa, school, workshop and boma cluster</t>
+          <t>Cambium ePMP Force 4525L subscriber radio, 25 dBi — main lodge, villas, spa, school, workshop and boma</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3237.08</v>
+        <v>3123.29</v>
       </c>
       <c r="E14" s="9">
         <f>C14*D14</f>
@@ -777,7 +771,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3237.08</v>
+        <v>3123.29</v>
       </c>
       <c r="E15" s="9">
         <f>C15*D15</f>
@@ -802,7 +796,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>530.67</v>
+        <v>512.01</v>
       </c>
       <c r="E16" s="9">
         <f>C16*D16</f>
@@ -823,7 +817,7 @@
         <v>1000</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>14.15</v>
+        <v>13.65</v>
       </c>
       <c r="E17" s="9">
         <f>C17*D17</f>
@@ -838,7 +832,7 @@
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Subtotal — B. Distribution — wireless links to buildings</t>
+          <t>Subtotal — Distribution — wireless links to buildings</t>
         </is>
       </c>
       <c r="E18" s="12">
@@ -846,12 +840,11 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>C. Wi-Fi and switching</t>
+          <t>Wi-Fi and switching</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -872,7 +865,7 @@
         <v>22</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1208.75</v>
+        <v>1166.26</v>
       </c>
       <c r="E21" s="9">
         <f>C21*D21</f>
@@ -897,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2222.92</v>
+        <v>2144.77</v>
       </c>
       <c r="E22" s="9">
         <f>C22*D22</f>
@@ -922,7 +915,7 @@
         <v>2</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2239.43</v>
+        <v>2160.7</v>
       </c>
       <c r="E23" s="9">
         <f>C23*D23</f>
@@ -943,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>766.52</v>
+        <v>739.58</v>
       </c>
       <c r="E24" s="9">
         <f>C24*D24</f>
@@ -964,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>707.5599999999999</v>
+        <v>682.6900000000001</v>
       </c>
       <c r="E25" s="9">
         <f>C25*D25</f>
@@ -975,7 +968,7 @@
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Subtotal — C. Wi-Fi and switching</t>
+          <t>Subtotal — Wi-Fi and switching</t>
         </is>
       </c>
       <c r="E26" s="12">
@@ -983,12 +976,11 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>D. Installation, commissioning and handover</t>
+          <t>Installation, commissioning and handover</t>
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -1009,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>5306.7</v>
+        <v>5120.15</v>
       </c>
       <c r="E29" s="9">
         <f>C29*D29</f>
@@ -1027,14 +1019,14 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Installation — two-technician team, mast, radios, access points, cabling and power</t>
+          <t>Installation — two-technician team: mast, radios, access points, cabling and power (25 buildings)</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>10613.39</v>
+        <v>10240.3</v>
       </c>
       <c r="E30" s="9">
         <f>C30*D30</f>
@@ -1059,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>5306.7</v>
+        <v>5120.15</v>
       </c>
       <c r="E31" s="9">
         <f>C31*D31</f>
@@ -1080,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2654.55</v>
+        <v>2563.81</v>
       </c>
       <c r="E32" s="9">
         <f>C32*D32</f>
@@ -1091,7 +1083,7 @@
     <row r="33">
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Subtotal — D. Installation, commissioning and handover</t>
+          <t>Subtotal — Installation, commissioning and handover</t>
         </is>
       </c>
       <c r="E33" s="12">
@@ -1099,7 +1091,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
         <is>
@@ -1133,7 +1124,6 @@
         <v/>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="16" t="inlineStr">
         <is>
@@ -1179,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1198,42 +1188,41 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Including VAT. Current figures from the lodge's August 2026 invoice. Proposed figures fixed for the 36-month agreement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Including VAT. Current figures from the lodge's August 2026 invoice, held flat. Proposed figures fixed for the 36-month agreement.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Excl. VAT</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Incl. VAT</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Today — current provider</t>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Current — today, current provider</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Business wireless 100 Mbps symmetrical (shared) + static IP</t>
         </is>
@@ -1252,7 +1241,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Rented Wi-Fi access points — 23 units on 12- and 24-month terms</t>
         </is>
@@ -1271,7 +1260,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Managed Wi-Fi service (2 sites)</t>
         </is>
@@ -1300,16 +1289,15 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>After the build — CTTX hybrid network</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Proposed — after the build, CTTX hybrid network</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Vodacom Business Connect 100 Mbps — uncontended 1:1, symmetrical, uncapped, unshaped, Business SLA, LTE backup, static IP (36-month term)</t>
         </is>
@@ -1327,8 +1315,8 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>CTTX managed service: remote monitoring, maintenance, quarterly site visits, priority support</t>
         </is>
@@ -1346,8 +1334,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Wi-Fi equipment rental</t>
         </is>
@@ -1380,7 +1368,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
@@ -1391,7 +1378,7 @@
         <f>B9-B15</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <f>C9-C15</f>
         <v/>
       </c>
@@ -1402,7 +1389,7 @@
           <t>Reduction in the monthly bill</t>
         </is>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <f>C17/C9</f>
         <v/>
       </c>
@@ -1421,103 +1408,86 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Once-off: Vodacom connection fee, payable when the link is installed</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>3129.4</v>
+      </c>
+      <c r="C20" s="15">
+        <f>B20*1.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>The 36-month agreement, with the build included</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Saving on the monthly bill over 36 months</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C23" s="15">
         <f>C17*36</f>
         <v/>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Once-off: Vodacom connection fee</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>3129.4</v>
-      </c>
-      <c r="C22" s="15">
-        <f>B22*1.15</f>
-        <v/>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>Payable once the link is installed</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>The 36-month agreement, with the build included</t>
-        </is>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Less: network build, paid up front (incl. VAT)</t>
+        </is>
+      </c>
+      <c r="C24" s="15">
+        <f>-'Detailed Cost Schedule'!E37</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saving on the monthly bill over 36 months</t>
+          <t>Less: Vodacom once-off connection fee (incl. VAT)</t>
         </is>
       </c>
       <c r="C25" s="15">
-        <f>C20</f>
+        <f>-C20</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Less: network build, paid up front (incl. VAT)</t>
-        </is>
-      </c>
-      <c r="C26" s="15">
-        <f>-'Detailed Cost Schedule'!E37</f>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Net position at the end of the 36 months — build fully paid, network owned</t>
+        </is>
+      </c>
+      <c r="C26" s="20">
+        <f>SUM(C23:C25)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Less: Vodacom once-off connection fee (incl. VAT)</t>
-        </is>
-      </c>
-      <c r="C27" s="15">
-        <f>-C22</f>
+          <t>Build and connection fee recovered from the saving after (months)</t>
+        </is>
+      </c>
+      <c r="C27" s="22">
+        <f>-(C24+C25)/C17</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Net position at the end of the 36 months — build fully paid, network owned</t>
-        </is>
-      </c>
-      <c r="C28" s="21">
-        <f>SUM(C25:C27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Build and connection fee recovered from the saving after (months)</t>
-        </is>
-      </c>
-      <c r="C29" s="24">
-        <f>-(C26+C27)/C17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Every year after that, at today's prices</t>
         </is>
       </c>
-      <c r="C30" s="15">
+      <c r="C28" s="15">
         <f>C17*12</f>
         <v/>
       </c>
@@ -1533,7 +1503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1551,12 +1521,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Including VAT. Option 2 is an illustration of an asset-finance facility the lodge would arrange directly with its bank or a finance house; CTTX is not the lender.</t>
+          <t>Including VAT. Option 2 illustrates an asset-finance facility the lodge would arrange directly with its bank or a finance house; CTTX is not the lender.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Option 1 — Buy outright</t>
         </is>
@@ -1623,13 +1593,13 @@
           <t>Build cost recovered from savings in (months)</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="22">
         <f>B5/B9</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Option 2 — Finance the build over 36 months (illustration)</t>
         </is>
@@ -1641,7 +1611,7 @@
           <t>Indicative interest rate p.a.</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="23" t="n">
         <v>0.12</v>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1710,7 +1680,7 @@
           <t>Difference per month (negative = less than today)</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="24">
         <f>B17-B18</f>
         <v/>
       </c>
@@ -1726,17 +1696,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Either way the lodge owns the mast, radios, Wi-Fi and power system; the only recurring items are the carrier link and CTTX support. The order is placed only once Vodacom has confirmed feasibility of the link to the mast position.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A22:C22"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
+++ b/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>25031.83</v>
+        <v>25006.79</v>
       </c>
       <c r="E6" s="9">
         <f>C6*D6</f>
@@ -631,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9637.26</v>
+        <v>9627.58</v>
       </c>
       <c r="E7" s="9">
         <f>C7*D7</f>
@@ -656,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>3651.23</v>
+        <v>3647.57</v>
       </c>
       <c r="E8" s="9">
         <f>C8*D8</f>
@@ -677,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>9102.49</v>
+        <v>9093.35</v>
       </c>
       <c r="E9" s="9">
         <f>C9*D9</f>
@@ -698,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>29527.12</v>
+        <v>29497.48</v>
       </c>
       <c r="E10" s="9">
         <f>C10*D10</f>
@@ -746,7 +746,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3123.29</v>
+        <v>3120.15</v>
       </c>
       <c r="E14" s="9">
         <f>C14*D14</f>
@@ -771,7 +771,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3123.29</v>
+        <v>3120.15</v>
       </c>
       <c r="E15" s="9">
         <f>C15*D15</f>
@@ -796,7 +796,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>512.01</v>
+        <v>511.5</v>
       </c>
       <c r="E16" s="9">
         <f>C16*D16</f>
@@ -817,7 +817,7 @@
         <v>1000</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>13.65</v>
+        <v>13.64</v>
       </c>
       <c r="E17" s="9">
         <f>C17*D17</f>
@@ -865,7 +865,7 @@
         <v>22</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1166.26</v>
+        <v>1165.09</v>
       </c>
       <c r="E21" s="9">
         <f>C21*D21</f>
@@ -890,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2144.77</v>
+        <v>2142.62</v>
       </c>
       <c r="E22" s="9">
         <f>C22*D22</f>
@@ -915,7 +915,7 @@
         <v>2</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2160.7</v>
+        <v>2158.53</v>
       </c>
       <c r="E23" s="9">
         <f>C23*D23</f>
@@ -936,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>739.58</v>
+        <v>738.83</v>
       </c>
       <c r="E24" s="9">
         <f>C24*D24</f>
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>682.6900000000001</v>
+        <v>682</v>
       </c>
       <c r="E25" s="9">
         <f>C25*D25</f>
@@ -980,7 +980,7 @@
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Installation, commissioning and handover</t>
+          <t>Installation and commissioning</t>
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -994,14 +994,14 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Site survey, RF design and link planning</t>
+          <t>Mast, base station, sector antennas, cabinet and solar power system — installation and commissioning (hours)</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>5120.15</v>
+        <v>750</v>
       </c>
       <c r="E29" s="9">
         <f>C29*D29</f>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Completed 22 Sep 2026</t>
+          <t>Two-technician team, at R750 per hour</t>
         </is>
       </c>
     </row>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Installation — two-technician team: mast, radios, access points, cabling and power (25 buildings)</t>
+          <t>Per building: subscriber radio mounted on the building, cable pulled in, Wi-Fi access point mounted on the ceiling and tested (28 buildings × 2 hours)</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>10240.3</v>
+        <v>750</v>
       </c>
       <c r="E30" s="9">
         <f>C30*D30</f>
@@ -1034,130 +1034,88 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Per day</t>
+          <t>At R750 per hour</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Commissioning, link testing and Wi-Fi coverage verification</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>5120.15</v>
-      </c>
-      <c r="E31" s="9">
-        <f>C31*D31</f>
-        <v/>
-      </c>
-      <c r="F31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Documentation, training and handover</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>2563.81</v>
-      </c>
-      <c r="E32" s="9">
-        <f>C32*D32</f>
-        <v/>
-      </c>
-      <c r="F32" s="10" t="inlineStr"/>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Subtotal — Installation and commissioning</t>
+        </is>
+      </c>
+      <c r="E31" s="12">
+        <f>SUM(E29:E30)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Subtotal — Installation, commissioning and handover</t>
-        </is>
-      </c>
-      <c r="E33" s="12">
-        <f>SUM(E29:E32)</f>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL — network build, excluding VAT</t>
+        </is>
+      </c>
+      <c r="E33" s="14">
+        <f>E11+E18+E26+E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>VAT at 15%</t>
+        </is>
+      </c>
+      <c r="E34" s="15">
+        <f>E33*0.15</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>TOTAL — network build, excluding VAT</t>
+          <t>TOTAL — network build, including VAT</t>
         </is>
       </c>
       <c r="E35" s="14">
-        <f>E11+E18+E26+E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>VAT at 15%</t>
-        </is>
-      </c>
-      <c r="E36" s="15">
-        <f>E35*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL — network build, including VAT</t>
-        </is>
-      </c>
-      <c r="E37" s="14">
-        <f>E35+E36</f>
-        <v/>
+        <f>E33+E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Payment terms: 50% on order (secures the equipment allocation and places the order), 50% on commissioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Ownership: all equipment, the mast, the cabinet and the power system are the property of Barefoot Addo Elephant Lodge (Pty) Ltd on handover.</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Payment terms: 50% on order (secures the equipment allocation and places the order), 50% on commissioning.</t>
+          <t>Included: delivery to site, installation, configuration and testing of every item above. Manufacturer warranties apply (Cambium 12 months; extended 2-year cover available as an option on request).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>Ownership: all equipment, the mast, the cabinet and the power system are the property of Barefoot Addo Elephant Lodge (Pty) Ltd on handover.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Included: design, delivery to site, installation, configuration, testing, documentation and training. Manufacturer warranties apply (Cambium 12 months; extended 2-year cover available as an option on request).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="16" t="inlineStr">
-        <is>
           <t>Not included: the Vodacom carrier link (see Monthly Costs), trenching or civil works beyond the mast plinth, Eskom connections, and any building works.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B38:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1444,7 +1402,7 @@
         </is>
       </c>
       <c r="C24" s="15">
-        <f>-'Detailed Cost Schedule'!E37</f>
+        <f>-'Detailed Cost Schedule'!E35</f>
         <v/>
       </c>
     </row>
@@ -1539,7 +1497,7 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <f>'Detailed Cost Schedule'!E37</f>
+        <f>'Detailed Cost Schedule'!E35</f>
         <v/>
       </c>
     </row>

--- a/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
+++ b/proposals/Barefoot_Detailed_Cost_Schedule_2026-09-29.xlsx
@@ -1257,11 +1257,11 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Vodacom Business Connect 100 Mbps — uncontended 1:1, symmetrical, uncapped, unshaped, Business SLA, LTE backup, static IP (36-month term)</t>
+          <t>Vodacom Business Connect 300 Mbps — uncontended 1:1, symmetrical, uncapped, unshaped, Business SLA, LTE backup, static IP (36-month term)</t>
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>4982.45</v>
+        <v>7812.55</v>
       </c>
       <c r="C12" s="15">
         <f>B12*1.15</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Carrier link, fixed for 36 months</t>
+          <t>Carrier link, fixed for 36 months. Three times the bandwidth of the current 100 Mbps shared service</t>
         </is>
       </c>
     </row>
